--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481252</v>
       </c>
       <c r="B2" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136193909</v>
       </c>
       <c r="B3" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136194146</v>
       </c>
       <c r="B4" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136194147</v>
       </c>
       <c r="B5" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136194148</v>
       </c>
       <c r="B6" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136194149</v>
       </c>
       <c r="B7" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136194150</v>
       </c>
       <c r="B8" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>136194157</v>
       </c>
       <c r="B9" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481252</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136193909</v>
       </c>
       <c r="B3" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136194146</v>
       </c>
       <c r="B4" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136194147</v>
       </c>
       <c r="B5" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136194148</v>
       </c>
       <c r="B6" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136194149</v>
       </c>
       <c r="B7" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136194150</v>
       </c>
       <c r="B8" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>136194157</v>
       </c>
       <c r="B9" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481252</v>
       </c>
       <c r="B2" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136193909</v>
       </c>
       <c r="B3" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136194146</v>
       </c>
       <c r="B4" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136194147</v>
       </c>
       <c r="B5" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136194148</v>
       </c>
       <c r="B6" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136194149</v>
       </c>
       <c r="B7" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136194150</v>
       </c>
       <c r="B8" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>136194157</v>
       </c>
       <c r="B9" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481252</v>
       </c>
       <c r="B2" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136193909</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136194146</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136194147</v>
       </c>
       <c r="B5" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136194148</v>
       </c>
       <c r="B6" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136194149</v>
       </c>
       <c r="B7" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>136194150</v>
       </c>
       <c r="B8" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>136194157</v>
       </c>
       <c r="B9" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481252</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481252</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481252</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481252</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35418-2026 artfynd.xlsx
+++ b/artfynd/A 35418-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481252</v>
       </c>
       <c r="B2" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
